--- a/morpg/morpg/Assets/TableData/Table_Species.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Species.xlsx
@@ -19,84 +19,78 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="26">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="24">
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Badrak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Selena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Teemole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kalapok</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Human</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Demon</x:t>
+  </x:si>
   <x:si>
     <x:t>Hidden</x:t>
   </x:si>
   <x:si>
+    <x:t>Machine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Species</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unknown</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sandora</x:t>
+  </x:si>
+  <x:si>
     <x:t>Toorka</x:t>
   </x:si>
   <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Default</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dragon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rodec</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Consume</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HiddenEnum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SpeciesEnum</x:t>
+  </x:si>
+  <x:si>
     <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Archmage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kalapok</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Human</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rodec</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Demon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Selena</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Teemole</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Required</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Badrak</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HiddenEnum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SpeciesEnum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Species</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Machine</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unknown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JobEnum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sandora</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Default</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -872,45 +866,45 @@
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F1" s="7"/>
       <x:c r="G1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F2" s="7"/>
       <x:c r="G2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -921,7 +915,7 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -934,17 +928,17 @@
       <x:c r="A5" s="1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>5</x:v>
+      <x:c r="B5" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="s">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E5" s="1">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="1"/>
@@ -953,34 +947,34 @@
       <x:c r="A6">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>6</x:v>
+      <x:c r="B6" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E6" s="1">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
       <x:c r="A7" s="1">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>1</x:v>
+      <x:c r="B7" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E7" s="1">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="7"/>
     </x:row>
@@ -988,17 +982,17 @@
       <x:c r="A8">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>10</x:v>
+      <x:c r="B8" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="1">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F8" s="8"/>
     </x:row>
@@ -1006,17 +1000,17 @@
       <x:c r="A9" s="1">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>8</x:v>
+      <x:c r="B9" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="1">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F9" s="7"/>
     </x:row>
@@ -1024,17 +1018,17 @@
       <x:c r="A10">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>25</x:v>
+      <x:c r="B10" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E10" s="1">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F10" s="8"/>
     </x:row>
@@ -1042,17 +1036,17 @@
       <x:c r="A11" s="1">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>20</x:v>
+      <x:c r="B11" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="s">
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="1">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F11" s="7"/>
     </x:row>
@@ -1060,17 +1054,17 @@
       <x:c r="A12">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>23</x:v>
+      <x:c r="B12" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="s">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E12" s="1">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F12" s="8"/>
     </x:row>
@@ -1078,17 +1072,17 @@
       <x:c r="A13" s="1">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="1" t="s">
-        <x:v>4</x:v>
+      <x:c r="B13" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E13">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F13" s="7"/>
     </x:row>
@@ -1096,30 +1090,54 @@
       <x:c r="A14">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E14" s="3" t="s">
-        <x:v>25</x:v>
+      <x:c r="B14" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C14" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D14" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E14" s="3">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F14" s="8"/>
     </x:row>
     <x:row r="15" spans="1:6">
-      <x:c r="A15" s="1"/>
-      <x:c r="B15" s="1"/>
-      <x:c r="C15" s="1"/>
+      <x:c r="A15" s="1">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B15" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C15" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D15" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E15">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="F15" s="7"/>
     </x:row>
-    <x:row r="16" spans="2:6">
-      <x:c r="B16" s="1"/>
-      <x:c r="C16" s="1"/>
-      <x:c r="E16" s="3"/>
+    <x:row r="16" spans="1:6">
+      <x:c r="A16">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B16" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C16" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="3">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="F16" s="8"/>
     </x:row>
     <x:row r="17" spans="1:6">
